--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1645,6 +1645,126 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122479207</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98202</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gustavslund, SSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>636794</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6546781</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskattat antal, växer tätt. Tio vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>122479207</v>
       </c>
       <c r="B10" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1664,11 +1664,6 @@
       </c>
       <c r="E10" t="n">
         <v>220787</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>122479207</v>
       </c>
       <c r="B10" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1665,6 +1665,11 @@
       <c r="E10" t="n">
         <v>220787</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1677,7 +1682,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1685,7 +1690,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1694,10 +1703,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636794</v>
+        <v>636806</v>
       </c>
       <c r="R10" t="n">
-        <v>6546781</v>
+        <v>6546784</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1734,7 +1743,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Uppskattat antal, växer tätt. Tio vinterståndare.</t>
+          <t>Återfynd. Tätväxande centralt. Tolv vinterståndare. Detta bestånd ligger närmast väg 57, där det för närvarande pågår arbete för breddning av vägen. Avstånd till markeringpinnar: 15-25 meter.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>122479207</v>
       </c>
       <c r="B10" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>122479207</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>122479207</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>122479207</v>
       </c>
       <c r="B10" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>122479207</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>122479207</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1769,6 +1769,130 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124788407</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gustavslund, SSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>636819</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6546759</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Återfynd. Ökat antal jämfört med 2022 (37 ex.).</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Ninna Werner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46237-2020 artfynd.xlsx
+++ b/artfynd/A 46237-2020 artfynd.xlsx
@@ -1774,7 +1774,7 @@
         <v>124788407</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
